--- a/artfynd/A 35887-2025 artfynd.xlsx
+++ b/artfynd/A 35887-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137386100</v>
       </c>
       <c r="B2" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137386138</v>
       </c>
       <c r="B3" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137385925</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137385936</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137385950</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137385957</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137386074</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137386106</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>137386223</v>
       </c>
       <c r="B10" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137386210</v>
       </c>
       <c r="B11" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 35887-2025 artfynd.xlsx
+++ b/artfynd/A 35887-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137386100</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137386138</v>
       </c>
       <c r="B3" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137385925</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137385936</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137385950</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137385957</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137386074</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137386106</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>137386223</v>
       </c>
       <c r="B10" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35887-2025 artfynd.xlsx
+++ b/artfynd/A 35887-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137386100</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137386138</v>
       </c>
       <c r="B3" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137385925</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137385936</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137385950</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137385957</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137386074</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137386106</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>137386223</v>
       </c>
       <c r="B10" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35887-2025 artfynd.xlsx
+++ b/artfynd/A 35887-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137386100</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137386138</v>
       </c>
       <c r="B3" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137385925</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137385936</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137385950</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137385957</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137386074</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137386106</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>137386223</v>
       </c>
       <c r="B10" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 35887-2025 artfynd.xlsx
+++ b/artfynd/A 35887-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137386100</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137386138</v>
       </c>
       <c r="B3" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>137385925</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>137385936</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>137385950</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137385957</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>137386074</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>137386106</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>137386223</v>
       </c>
       <c r="B10" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137386210</v>
       </c>
       <c r="B11" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
